--- a/data/trans_orig/IP31KM14_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM14_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19680</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12909</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27834</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16244</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10429</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26685</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43886</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>24108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58770</t>
+          <t>44620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>101529</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93375</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>108300</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>85465</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75024</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91280</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>109180</t>
+          <t>86376</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91290</t>
+          <t>79351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118029</t>
+          <t>91400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>194646</t>
+          <t>187905</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178116</t>
+          <t>176938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206258</t>
+          <t>197450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18637</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11989</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25882</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16075</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10659</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23265</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35726</t>
+          <t>35450</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>45748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71243</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63998</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77891</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>77317</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>70127</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82733</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>74057</t>
+          <t>78597</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66218</t>
+          <t>70849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79888</t>
+          <t>84583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>151375</t>
+          <t>149840</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141619</t>
+          <t>139542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>160325</t>
+          <t>158061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>29143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46491</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41490</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50867</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>40168</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34083</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>44346</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,19%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>68,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52211</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>34622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56873</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>92379</t>
+          <t>87787</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83787</t>
+          <t>78711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99095</t>
+          <t>94390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41231</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30390</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52666</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31494</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19805</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>42681</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>30130</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55466</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>74169</t>
+          <t>71361</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57562</t>
+          <t>57967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91772</t>
+          <t>85030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>144647</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166923</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>184043</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>172856</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>195732</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>169983</t>
+          <t>146510</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157192</t>
+          <t>136497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180516</t>
+          <t>153707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>354027</t>
+          <t>302592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336424</t>
+          <t>288923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370634</t>
+          <t>315986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27366</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19071</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37363</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23656</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16583</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31679</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30605</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42871</t>
+          <t>32969</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>51813</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41766</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68042</t>
+          <t>64237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>118220</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>108223</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>126515</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>91853</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>83830</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>98926</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>79,52%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>72,57%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>128856</t>
+          <t>91020</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116590</t>
+          <t>82497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138017</t>
+          <t>98052</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>220709</t>
+          <t>209239</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>206928</t>
+          <t>196815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233204</t>
+          <t>220810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>16791</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>11508</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>24510</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>35,58%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>23778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>30980</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59553</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>54144</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>62858</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>90,42%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>52104</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>44385</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>57387</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>64,42%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62557</t>
+          <t>54237</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57462</t>
+          <t>46578</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66000</t>
+          <t>59830</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>114660</t>
+          <t>113790</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106223</t>
+          <t>105240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121706</t>
+          <t>120892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,75%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>122578</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>104173</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>142469</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>114180</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>94890</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>134072</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,78%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>135524</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113642</t>
+          <t>96730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156541</t>
+          <t>130270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>249704</t>
+          <t>234773</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>222911</t>
+          <t>210029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282677</t>
+          <t>259038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>553117</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>533226</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>571522</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>81,86%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>78,92%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>84,58%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>745</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>530951</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>511059</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>550241</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>82,3%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>79,22%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>85,29%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>596844</t>
+          <t>498037</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>575827</t>
+          <t>479962</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>618726</t>
+          <t>513502</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1051154</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1094822</t>
+          <t>1026889</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1154588</t>
+          <t>1075898</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
